--- a/Wagnon_Paysage_Outil_Patron_V9.xlsx
+++ b/Wagnon_Paysage_Outil_Patron_V9.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5031940-AB12-4059-955E-B1ACBC217C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7FFDC31-134D-437B-989B-DA8804E8B9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="132">
   <si>
     <t>WAGNON PAYSAGE — MODE CHANTIER</t>
   </si>
@@ -57,10 +57,19 @@
     <t>Nom du client</t>
   </si>
   <si>
+    <t xml:space="preserve">Wagnon </t>
+  </si>
+  <si>
     <t>Adresse</t>
   </si>
   <si>
+    <t xml:space="preserve">6 avenue marc Francina </t>
+  </si>
+  <si>
     <t>Téléphone</t>
+  </si>
+  <si>
+    <t>07 84 31 26 42</t>
   </si>
   <si>
     <t>Distance aller (km)</t>
@@ -1252,7 +1261,7 @@
     <col min="3" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="25.5">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1264,23 +1273,29 @@
       <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12"/>
+      <c r="B3" s="12" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="12"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="11" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" s="12">
         <v>0</v>
@@ -1288,7 +1303,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" s="12">
         <v>0</v>
@@ -1296,7 +1311,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" s="12">
         <v>0</v>
@@ -1304,75 +1319,75 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18.75">
       <c r="A13" s="13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B14" s="12">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" ht="18">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B15" s="14">
         <f>B7*B14</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" ht="18.75">
       <c r="A17" s="13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18.75">
       <c r="A23" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -1416,15 +1431,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B2" s="10">
         <v>600</v>
@@ -1432,7 +1447,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B3" s="10">
         <v>1.5</v>
@@ -1440,7 +1455,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B4" s="10">
         <v>20</v>
@@ -1448,7 +1463,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B5" s="10">
         <v>0</v>
@@ -1456,7 +1471,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B6" s="10">
         <v>0</v>
@@ -1464,7 +1479,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B8">
         <f>ROUND((B3*Paramètres!B2+B4*Paramètres!B3+B5+B6)*(1+Paramètres!B4/100)/5,0)*5</f>
@@ -1473,7 +1488,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B9">
         <f>IF(B2=0,0,B8/B2)</f>
@@ -1496,15 +1511,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B2" s="10">
         <v>500</v>
@@ -1512,7 +1527,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B3" s="10">
         <v>3</v>
@@ -1520,7 +1535,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B4" s="10">
         <v>20</v>
@@ -1528,7 +1543,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B5" s="10">
         <v>30</v>
@@ -1536,7 +1551,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B7">
         <f>ROUND((B3*Paramètres!B2+B4*Paramètres!B3+B5)*(1+Paramètres!B4/100)/5,0)*5</f>
@@ -1545,7 +1560,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B8">
         <f>IF(B2=0,0,B7/B2)</f>
@@ -1568,15 +1583,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B2" s="10">
         <v>300</v>
@@ -1584,7 +1599,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B3" s="10">
         <v>3</v>
@@ -1592,7 +1607,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B4" s="10">
         <v>20</v>
@@ -1600,7 +1615,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B5" s="10">
         <v>30</v>
@@ -1608,7 +1623,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B7">
         <f>ROUND((B2*(1+Paramètres!B5/100)+B3*Paramètres!B2+B4*Paramètres!B3+B5)*(1+Paramètres!B4/100)/5,0)*5</f>
@@ -1633,16 +1648,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="15" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1657,19 +1672,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="15" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1693,31 +1708,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B3" s="10">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B4" s="10">
         <v>1.8</v>
@@ -1725,7 +1740,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B5" s="10">
         <v>3</v>
@@ -1733,7 +1748,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B6" s="10">
         <v>1</v>
@@ -1741,15 +1756,15 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B7" s="10">
-        <v>2.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B8" s="10">
         <v>1</v>
@@ -1757,23 +1772,23 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B9" s="10">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B10" s="10">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B11" s="10">
         <v>0</v>
@@ -1781,39 +1796,39 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B15">
         <f>B7*B6+B8</f>
-        <v>3.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B16">
         <f>B15*Paramètres!B2</f>
-        <v>175</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B17">
         <f>B9*Paramètres!B3</f>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B18">
         <f>B11*Paramètres!B5/100</f>
@@ -1822,55 +1837,55 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B19">
         <f>B16+B17+B10+B11</f>
-        <v>210</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B20">
         <f>B19*Paramètres!B4/100</f>
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B21">
         <f>B19+B20+B18</f>
-        <v>231</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B22">
         <f>ROUND(B21/5,0)*5</f>
-        <v>230</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B23">
         <f>IF(B3=0,0,B22/B3)</f>
-        <v>6.2162162162162158</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="41.25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1889,15 +1904,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2">
         <v>50</v>
@@ -1905,7 +1920,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2">
         <v>0.5</v>
@@ -1913,7 +1928,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2">
         <v>10</v>
@@ -1921,7 +1936,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2">
         <v>20</v>
@@ -1929,7 +1944,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
         <v>50000</v>
@@ -1937,7 +1952,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2">
         <v>4167</v>
@@ -1953,10 +1968,10 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1975,23 +1990,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B3" s="4">
         <v>4</v>
@@ -1999,7 +2014,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B4" s="4">
         <v>20</v>
@@ -2007,7 +2022,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
         <v>25</v>
@@ -2015,7 +2030,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4">
         <v>0</v>
@@ -2023,7 +2038,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B7" s="4">
         <v>20</v>
@@ -2039,13 +2054,13 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2">
         <f>B3*Paramètres!B2</f>
@@ -2054,7 +2069,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2">
         <f>B4*Paramètres!B3</f>
@@ -2063,7 +2078,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2">
         <f>B6*Paramètres!B5/100</f>
@@ -2072,7 +2087,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2">
         <f>SUM(B11:B13)+B5+B6</f>
@@ -2081,7 +2096,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2">
         <f>B14*Paramètres!B4/100</f>
@@ -2090,16 +2105,16 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2">
         <f>B14+B15</f>
         <v>258.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" ht="18.75">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B17" s="5">
         <f>ROUND(B16/5,0)*5</f>
@@ -2112,7 +2127,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B19" s="2">
         <f>B14</f>
@@ -2125,10 +2140,10 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2146,37 +2161,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2200,37 +2215,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -11754,21 +11769,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2">
@@ -11782,7 +11797,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2">
@@ -11796,7 +11811,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2">
@@ -11810,7 +11825,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2">
@@ -11824,7 +11839,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -11838,7 +11853,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
@@ -11852,7 +11867,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -11866,7 +11881,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -11880,7 +11895,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -11894,7 +11909,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -11908,7 +11923,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2">
@@ -11922,7 +11937,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
@@ -11942,7 +11957,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B15" s="3">
         <f>SUM(B2:B13)</f>
@@ -11973,22 +11988,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -12011,15 +12026,15 @@
     <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="21">
       <c r="A1" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B2" s="7">
         <f>Paramètres!B6</f>
@@ -12028,7 +12043,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B3" s="7">
         <f>SUM('CA mensuel'!B2:B13)</f>
@@ -12037,7 +12052,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B4" s="7">
         <f>B2-B3</f>
@@ -12046,7 +12061,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B5" s="7">
         <f>COUNTA(Clients!A2:A500)</f>
@@ -12055,7 +12070,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B6" s="7">
         <f>COUNTA(Devis!A2:A500)</f>
@@ -12064,7 +12079,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B7" s="7">
         <f>COUNTIF(Devis!K2:K500,"Accepté")</f>
@@ -12073,7 +12088,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B8" s="8">
         <f>IF(B6=0,0,B7/B6)</f>
@@ -12082,19 +12097,19 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B9" s="7">
         <f>SUM(Frais!D2:D1000)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="54.75">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Wagnon_Paysage_Outil_Patron_V9.xlsx
+++ b/Wagnon_Paysage_Outil_Patron_V9.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7FFDC31-134D-437B-989B-DA8804E8B9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BCE9CAD-350C-7B4A-A9D8-4371C2F628A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode Chantier V9" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
   <si>
     <t>WAGNON PAYSAGE — MODE CHANTIER</t>
   </si>
@@ -57,394 +57,388 @@
     <t>Nom du client</t>
   </si>
   <si>
+    <t>Adresse</t>
+  </si>
+  <si>
+    <t>Téléphone</t>
+  </si>
+  <si>
+    <t>Distance aller (km)</t>
+  </si>
+  <si>
+    <t>Longueur de haie (m)</t>
+  </si>
+  <si>
+    <t>Hauteur de haie (m)</t>
+  </si>
+  <si>
+    <t>Évacuation des déchets</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
+    <t>Nettoyage fin de chantier</t>
+  </si>
+  <si>
+    <t>ESTIMATION RAPIDE</t>
+  </si>
+  <si>
+    <t>Prix conseillé taille de haie (€/m)</t>
+  </si>
+  <si>
+    <t>Montant estimé HT</t>
+  </si>
+  <si>
+    <t>Check-list avant départ</t>
+  </si>
+  <si>
+    <t>✓ Photos avant chantier</t>
+  </si>
+  <si>
+    <t>✓ Validation du client</t>
+  </si>
+  <si>
+    <t>✓ Matériel chargé</t>
+  </si>
+  <si>
+    <t>✓ Déchets prévus</t>
+  </si>
+  <si>
+    <t>WAGNON PAYSAGE – DEVIS TERRAIN V3</t>
+  </si>
+  <si>
+    <t>Valeur</t>
+  </si>
+  <si>
+    <t>Prestation</t>
+  </si>
+  <si>
+    <t>Taille de haie</t>
+  </si>
+  <si>
+    <t>Mètres linéaires</t>
+  </si>
+  <si>
+    <t>Hauteur (m)</t>
+  </si>
+  <si>
+    <t>Faces à tailler</t>
+  </si>
+  <si>
+    <t>État / difficulté (1=facile, 1.25=difficile)</t>
+  </si>
+  <si>
+    <t>Temps de base (h)</t>
+  </si>
+  <si>
+    <t>Temps nettoyage/chargement (h)</t>
+  </si>
+  <si>
+    <t>Km aller-retour</t>
+  </si>
+  <si>
+    <t>Déchets verts (€)</t>
+  </si>
+  <si>
+    <t>Fournitures (€)</t>
+  </si>
+  <si>
+    <t>CALCUL AUTOMATIQUE</t>
+  </si>
+  <si>
+    <t>Temps de travail estimé (h)</t>
+  </si>
+  <si>
+    <t>Main-d'œuvre (€)</t>
+  </si>
+  <si>
+    <t>Déplacement (€)</t>
+  </si>
+  <si>
+    <t>Marge fournitures (€)</t>
+  </si>
+  <si>
+    <t>Coût direct estimé (€)</t>
+  </si>
+  <si>
+    <t>Marge sécurité (€)</t>
+  </si>
+  <si>
+    <t>PRIX CONSEILLÉ (€)</t>
+  </si>
+  <si>
+    <t>PRIX ARRONDI (€)</t>
+  </si>
+  <si>
+    <t>Prix / mètre linéaire (€)</t>
+  </si>
+  <si>
+    <t>Conseil</t>
+  </si>
+  <si>
+    <t>Le temps de base est à adapter après tes premiers chantiers : note le temps réel, puis ajuste tes références.</t>
+  </si>
+  <si>
+    <t>WAGNON PAYSAGE – PARAMÈTRES</t>
+  </si>
+  <si>
+    <t>Tarif interne cible €/h</t>
+  </si>
+  <si>
+    <t>Coût véhicule €/km</t>
+  </si>
+  <si>
+    <t>Marge sécurité %</t>
+  </si>
+  <si>
+    <t>Marge fournitures %</t>
+  </si>
+  <si>
+    <t>Objectif CA annuel</t>
+  </si>
+  <si>
+    <t>Objectif CA mensuel</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>Les taux sont des hypothèses de pilotage. À valider avec ton comptable selon ton statut et tes coûts réels.</t>
+  </si>
+  <si>
+    <t>WAGNON PAYSAGE – CALCULETTE DEVIS</t>
+  </si>
+  <si>
+    <t>Haie</t>
+  </si>
+  <si>
+    <t>Temps de travail (h)</t>
+  </si>
+  <si>
+    <t>Déchets / déchèterie (€)</t>
+  </si>
+  <si>
+    <t>Quantité / unités (info)</t>
+  </si>
+  <si>
+    <t>CALCUL</t>
+  </si>
+  <si>
+    <t>Main-d'œuvre</t>
+  </si>
+  <si>
+    <t>Déplacement</t>
+  </si>
+  <si>
+    <t>Marge fournitures</t>
+  </si>
+  <si>
+    <t>Sous-total</t>
+  </si>
+  <si>
+    <t>Marge sécurité</t>
+  </si>
+  <si>
+    <t>PRIX CONSEILLÉ</t>
+  </si>
+  <si>
+    <t>PRIX ARRONDI</t>
+  </si>
+  <si>
+    <t>Prix minimum à discuter</t>
+  </si>
+  <si>
+    <t>Mode d'emploi</t>
+  </si>
+  <si>
+    <t>Modifie uniquement les cellules jaunes/bleues d'entrée. Les cellules de calcul se mettent à jour automatiquement.</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Ville</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Prix devis</t>
+  </si>
+  <si>
+    <t>Date devis</t>
+  </si>
+  <si>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>Dernier passage</t>
+  </si>
+  <si>
+    <t>Prochain passage</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>N° devis</t>
+  </si>
+  <si>
+    <t>Temps h</t>
+  </si>
+  <si>
+    <t>Km A/R</t>
+  </si>
+  <si>
+    <t>Déchets €</t>
+  </si>
+  <si>
+    <t>Fournitures €</t>
+  </si>
+  <si>
+    <t>Prix conseillé €</t>
+  </si>
+  <si>
+    <t>Prix vendu €</t>
+  </si>
+  <si>
+    <t>Marge brute estimée €</t>
+  </si>
+  <si>
+    <t>Mois</t>
+  </si>
+  <si>
+    <t>CA réalisé €</t>
+  </si>
+  <si>
+    <t>Objectif €</t>
+  </si>
+  <si>
+    <t>Écart €</t>
+  </si>
+  <si>
+    <t>Janvier</t>
+  </si>
+  <si>
+    <t>Février</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>Avril</t>
+  </si>
+  <si>
+    <t>Mai</t>
+  </si>
+  <si>
+    <t>Juin</t>
+  </si>
+  <si>
+    <t>Juillet</t>
+  </si>
+  <si>
+    <t>Août</t>
+  </si>
+  <si>
+    <t>Septembre</t>
+  </si>
+  <si>
+    <t>Octobre</t>
+  </si>
+  <si>
+    <t>Novembre</t>
+  </si>
+  <si>
+    <t>Décembre</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Catégorie</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Montant €</t>
+  </si>
+  <si>
+    <t>Professionnel ?</t>
+  </si>
+  <si>
+    <t>WAGNON PAYSAGE – TABLEAU DE BORD PATRON</t>
+  </si>
+  <si>
+    <t>CA saisi à ce jour</t>
+  </si>
+  <si>
+    <t>Reste à faire</t>
+  </si>
+  <si>
+    <t>Clients enregistrés</t>
+  </si>
+  <si>
+    <t>Devis enregistrés</t>
+  </si>
+  <si>
+    <t>Devis acceptés</t>
+  </si>
+  <si>
+    <t>Taux d'acceptation</t>
+  </si>
+  <si>
+    <t>Total frais saisis</t>
+  </si>
+  <si>
+    <t>Utilise 'Devis terrain' pour les haies, puis les onglets Tonte, Débroussaillage ou Plantation selon le chantier.</t>
+  </si>
+  <si>
+    <t>WAGNON PAYSAGE – TONTE</t>
+  </si>
+  <si>
+    <t>Surface m²</t>
+  </si>
+  <si>
+    <t>Temps estimé h</t>
+  </si>
+  <si>
+    <t>Prix conseillé</t>
+  </si>
+  <si>
+    <t>Prix / m²</t>
+  </si>
+  <si>
+    <t>WAGNON PAYSAGE – DÉBROUSSAILLAGE</t>
+  </si>
+  <si>
+    <t>WAGNON PAYSAGE – PLANTATION</t>
+  </si>
+  <si>
+    <t>Autres coûts €</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>N°</t>
+  </si>
+  <si>
+    <t>Montant TTC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wagnon </t>
   </si>
   <si>
-    <t>Adresse</t>
-  </si>
-  <si>
     <t xml:space="preserve">6 avenue marc Francina </t>
   </si>
   <si>
-    <t>Téléphone</t>
-  </si>
-  <si>
     <t>07 84 31 26 42</t>
-  </si>
-  <si>
-    <t>Distance aller (km)</t>
-  </si>
-  <si>
-    <t>Longueur de haie (m)</t>
-  </si>
-  <si>
-    <t>Hauteur de haie (m)</t>
-  </si>
-  <si>
-    <t>Évacuation des déchets</t>
-  </si>
-  <si>
-    <t>Oui</t>
-  </si>
-  <si>
-    <t>Nettoyage fin de chantier</t>
-  </si>
-  <si>
-    <t>ESTIMATION RAPIDE</t>
-  </si>
-  <si>
-    <t>Prix conseillé taille de haie (€/m)</t>
-  </si>
-  <si>
-    <t>Montant estimé HT</t>
-  </si>
-  <si>
-    <t>Check-list avant départ</t>
-  </si>
-  <si>
-    <t>✓ Photos avant chantier</t>
-  </si>
-  <si>
-    <t>✓ Validation du client</t>
-  </si>
-  <si>
-    <t>✓ Matériel chargé</t>
-  </si>
-  <si>
-    <t>✓ Déchets prévus</t>
-  </si>
-  <si>
-    <t>PROCHAINE ÉTAPE (V10)</t>
-  </si>
-  <si>
-    <t>Cette feuille est pensée pour le téléphone. La prochaine version intégrera un bouton Excel (macro VBA) qui générera automatiquement le PDF, incrémentera le numéro de devis et alimentera le suivi des devis.</t>
-  </si>
-  <si>
-    <t>WAGNON PAYSAGE – DEVIS TERRAIN V3</t>
-  </si>
-  <si>
-    <t>Valeur</t>
-  </si>
-  <si>
-    <t>Prestation</t>
-  </si>
-  <si>
-    <t>Taille de haie</t>
-  </si>
-  <si>
-    <t>Mètres linéaires</t>
-  </si>
-  <si>
-    <t>Hauteur (m)</t>
-  </si>
-  <si>
-    <t>Faces à tailler</t>
-  </si>
-  <si>
-    <t>État / difficulté (1=facile, 1.25=difficile)</t>
-  </si>
-  <si>
-    <t>Temps de base (h)</t>
-  </si>
-  <si>
-    <t>Temps nettoyage/chargement (h)</t>
-  </si>
-  <si>
-    <t>Km aller-retour</t>
-  </si>
-  <si>
-    <t>Déchets verts (€)</t>
-  </si>
-  <si>
-    <t>Fournitures (€)</t>
-  </si>
-  <si>
-    <t>CALCUL AUTOMATIQUE</t>
-  </si>
-  <si>
-    <t>Temps de travail estimé (h)</t>
-  </si>
-  <si>
-    <t>Main-d'œuvre (€)</t>
-  </si>
-  <si>
-    <t>Déplacement (€)</t>
-  </si>
-  <si>
-    <t>Marge fournitures (€)</t>
-  </si>
-  <si>
-    <t>Coût direct estimé (€)</t>
-  </si>
-  <si>
-    <t>Marge sécurité (€)</t>
-  </si>
-  <si>
-    <t>PRIX CONSEILLÉ (€)</t>
-  </si>
-  <si>
-    <t>PRIX ARRONDI (€)</t>
-  </si>
-  <si>
-    <t>Prix / mètre linéaire (€)</t>
-  </si>
-  <si>
-    <t>Conseil</t>
-  </si>
-  <si>
-    <t>Le temps de base est à adapter après tes premiers chantiers : note le temps réel, puis ajuste tes références.</t>
-  </si>
-  <si>
-    <t>WAGNON PAYSAGE – PARAMÈTRES</t>
-  </si>
-  <si>
-    <t>Tarif interne cible €/h</t>
-  </si>
-  <si>
-    <t>Coût véhicule €/km</t>
-  </si>
-  <si>
-    <t>Marge sécurité %</t>
-  </si>
-  <si>
-    <t>Marge fournitures %</t>
-  </si>
-  <si>
-    <t>Objectif CA annuel</t>
-  </si>
-  <si>
-    <t>Objectif CA mensuel</t>
-  </si>
-  <si>
-    <t>Important</t>
-  </si>
-  <si>
-    <t>Les taux sont des hypothèses de pilotage. À valider avec ton comptable selon ton statut et tes coûts réels.</t>
-  </si>
-  <si>
-    <t>WAGNON PAYSAGE – CALCULETTE DEVIS</t>
-  </si>
-  <si>
-    <t>Haie</t>
-  </si>
-  <si>
-    <t>Temps de travail (h)</t>
-  </si>
-  <si>
-    <t>Déchets / déchèterie (€)</t>
-  </si>
-  <si>
-    <t>Quantité / unités (info)</t>
-  </si>
-  <si>
-    <t>CALCUL</t>
-  </si>
-  <si>
-    <t>Main-d'œuvre</t>
-  </si>
-  <si>
-    <t>Déplacement</t>
-  </si>
-  <si>
-    <t>Marge fournitures</t>
-  </si>
-  <si>
-    <t>Sous-total</t>
-  </si>
-  <si>
-    <t>Marge sécurité</t>
-  </si>
-  <si>
-    <t>PRIX CONSEILLÉ</t>
-  </si>
-  <si>
-    <t>PRIX ARRONDI</t>
-  </si>
-  <si>
-    <t>Prix minimum à discuter</t>
-  </si>
-  <si>
-    <t>Mode d'emploi</t>
-  </si>
-  <si>
-    <t>Modifie uniquement les cellules jaunes/bleues d'entrée. Les cellules de calcul se mettent à jour automatiquement.</t>
-  </si>
-  <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>Ville</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Prix devis</t>
-  </si>
-  <si>
-    <t>Date devis</t>
-  </si>
-  <si>
-    <t>Statut</t>
-  </si>
-  <si>
-    <t>Dernier passage</t>
-  </si>
-  <si>
-    <t>Prochain passage</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>N° devis</t>
-  </si>
-  <si>
-    <t>Temps h</t>
-  </si>
-  <si>
-    <t>Km A/R</t>
-  </si>
-  <si>
-    <t>Déchets €</t>
-  </si>
-  <si>
-    <t>Fournitures €</t>
-  </si>
-  <si>
-    <t>Prix conseillé €</t>
-  </si>
-  <si>
-    <t>Prix vendu €</t>
-  </si>
-  <si>
-    <t>Marge brute estimée €</t>
-  </si>
-  <si>
-    <t>Mois</t>
-  </si>
-  <si>
-    <t>CA réalisé €</t>
-  </si>
-  <si>
-    <t>Objectif €</t>
-  </si>
-  <si>
-    <t>Écart €</t>
-  </si>
-  <si>
-    <t>Janvier</t>
-  </si>
-  <si>
-    <t>Février</t>
-  </si>
-  <si>
-    <t>Mars</t>
-  </si>
-  <si>
-    <t>Avril</t>
-  </si>
-  <si>
-    <t>Mai</t>
-  </si>
-  <si>
-    <t>Juin</t>
-  </si>
-  <si>
-    <t>Juillet</t>
-  </si>
-  <si>
-    <t>Août</t>
-  </si>
-  <si>
-    <t>Septembre</t>
-  </si>
-  <si>
-    <t>Octobre</t>
-  </si>
-  <si>
-    <t>Novembre</t>
-  </si>
-  <si>
-    <t>Décembre</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Catégorie</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Montant €</t>
-  </si>
-  <si>
-    <t>Professionnel ?</t>
-  </si>
-  <si>
-    <t>WAGNON PAYSAGE – TABLEAU DE BORD PATRON</t>
-  </si>
-  <si>
-    <t>CA saisi à ce jour</t>
-  </si>
-  <si>
-    <t>Reste à faire</t>
-  </si>
-  <si>
-    <t>Clients enregistrés</t>
-  </si>
-  <si>
-    <t>Devis enregistrés</t>
-  </si>
-  <si>
-    <t>Devis acceptés</t>
-  </si>
-  <si>
-    <t>Taux d'acceptation</t>
-  </si>
-  <si>
-    <t>Total frais saisis</t>
-  </si>
-  <si>
-    <t>Utilise 'Devis terrain' pour les haies, puis les onglets Tonte, Débroussaillage ou Plantation selon le chantier.</t>
-  </si>
-  <si>
-    <t>WAGNON PAYSAGE – TONTE</t>
-  </si>
-  <si>
-    <t>Surface m²</t>
-  </si>
-  <si>
-    <t>Temps estimé h</t>
-  </si>
-  <si>
-    <t>Prix conseillé</t>
-  </si>
-  <si>
-    <t>Prix / m²</t>
-  </si>
-  <si>
-    <t>WAGNON PAYSAGE – DÉBROUSSAILLAGE</t>
-  </si>
-  <si>
-    <t>WAGNON PAYSAGE – PLANTATION</t>
-  </si>
-  <si>
-    <t>Autres coûts €</t>
-  </si>
-  <si>
-    <t>Nom</t>
-  </si>
-  <si>
-    <t>N°</t>
-  </si>
-  <si>
-    <t>Montant TTC</t>
   </si>
 </sst>
 </file>
@@ -454,7 +448,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -575,21 +569,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1253,15 +1244,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="4" width="22" customWidth="1"/>
+    <col min="1" max="1" width="27.98046875" customWidth="1"/>
+    <col min="2" max="2" width="23.9453125" customWidth="1"/>
+    <col min="3" max="4" width="22.05859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.5">
+    <row r="1" spans="1:4" ht="25.5" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1269,152 +1260,120 @@
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="11" t="s">
+      <c r="B4" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B5" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="11" t="s">
+      <c r="B6" s="13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B7" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="11" t="s">
+      <c r="B8" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="11" t="s">
+      <c r="B9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="11" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="11" t="s">
+      <c r="B10" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="12" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="11" t="s">
+      <c r="B14" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="18.75">
-      <c r="A13" s="13" t="s">
+      <c r="B15" s="15">
+        <f>B7*B14</f>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="18">
-      <c r="A15" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="14">
-        <f>B7*B14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="18.75">
-      <c r="A17" s="13" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="18.75">
-      <c r="A23" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A24:D27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1423,72 +1382,72 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="1" max="1" width="27.98046875" customWidth="1"/>
+    <col min="2" max="2" width="25.01953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B2" s="10">
         <v>600</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B3" s="10">
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B4" s="10">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B5" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B6" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B8">
         <f>ROUND((B3*Paramètres!B2+B4*Paramètres!B3+B5+B6)*(1+Paramètres!B4/100)/5,0)*5</f>
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B9">
         <f>IF(B2=0,0,B8/B2)</f>
@@ -1503,64 +1462,64 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="1" max="1" width="32.015625" customWidth="1"/>
+    <col min="2" max="2" width="25.01953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B2" s="10">
         <v>500</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B3" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B4" s="10">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B5" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B7">
         <f>ROUND((B3*Paramètres!B2+B4*Paramètres!B3+B5)*(1+Paramètres!B4/100)/5,0)*5</f>
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B8">
         <f>IF(B2=0,0,B7/B2)</f>
@@ -1575,55 +1534,55 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="1" max="1" width="29.99609375" customWidth="1"/>
+    <col min="2" max="2" width="25.01953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B2" s="10">
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B3" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B4" s="10">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B5" s="10">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B7">
         <f>ROUND((B2*(1+Paramètres!B5/100)+B3*Paramètres!B2+B4*Paramètres!B3+B5)*(1+Paramètres!B4/100)/5,0)*5</f>
@@ -1638,26 +1597,26 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="1" max="1" width="27.98046875" customWidth="1"/>
+    <col min="2" max="2" width="34.03125" customWidth="1"/>
+    <col min="3" max="3" width="18.0234375" customWidth="1"/>
+    <col min="4" max="4" width="27.98046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="15" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>75</v>
+      <c r="D1" s="16" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1668,23 +1627,23 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1" s="15" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>73</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1700,192 +1659,192 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="1" max="1" width="41.96875" customWidth="1"/>
+    <col min="2" max="2" width="32.015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B4" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="10">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="10">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>29</v>
       </c>
       <c r="B5" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B6" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B7" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B8" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B9" s="10">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B10" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B11" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B15">
         <f>B7*B6+B8</f>
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B16">
         <f>B15*Paramètres!B2</f>
         <v>300</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B17">
         <f>B9*Paramètres!B3</f>
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B18">
         <f>B11*Paramètres!B5/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B19">
         <f>B16+B17+B10+B11</f>
         <v>420</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B20">
         <f>B19*Paramètres!B4/100</f>
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B21">
         <f>B19+B20+B18</f>
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B22">
         <f>ROUND(B21/5,0)*5</f>
         <v>460</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B23">
         <f>IF(B3=0,0,B22/B3)</f>
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="41.25">
+        <v>10.222222222222221</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1896,82 +1855,82 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="1" max="1" width="32.015625" customWidth="1"/>
+    <col min="2" max="2" width="69.94921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2">
         <v>50000</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2">
         <v>4167</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1982,168 +1941,168 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="1" max="1" width="29.99609375" customWidth="1"/>
+    <col min="2" max="2" width="27.98046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B3" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B4" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B6" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2">
         <f>B3*Paramètres!B2</f>
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2">
         <f>B4*Paramètres!B3</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2">
         <f>B6*Paramètres!B5/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2">
         <f>SUM(B11:B13)+B5+B6</f>
         <v>235</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2">
         <f>B14*Paramètres!B4/100</f>
         <v>23.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2">
         <f>B14+B15</f>
         <v>258.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18.75">
+    <row r="17" spans="1:2" ht="18.75" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B17" s="5">
         <f>ROUND(B16/5,0)*5</f>
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2">
         <f>B14</f>
         <v>235</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2154,44 +2113,44 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="11" width="18" customWidth="1"/>
+    <col min="1" max="11" width="18.0234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2208,47 +2167,47 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K501"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="11" width="18" customWidth="1"/>
+    <col min="1" max="11" width="18.0234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2267,7 +2226,7 @@
       </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2286,7 +2245,7 @@
       </c>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2305,7 +2264,7 @@
       </c>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2324,7 +2283,7 @@
       </c>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2343,7 +2302,7 @@
       </c>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2362,7 +2321,7 @@
       </c>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2381,7 +2340,7 @@
       </c>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2400,7 +2359,7 @@
       </c>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -2419,7 +2378,7 @@
       </c>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2438,7 +2397,7 @@
       </c>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2457,7 +2416,7 @@
       </c>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2476,7 +2435,7 @@
       </c>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2495,7 +2454,7 @@
       </c>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2514,7 +2473,7 @@
       </c>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2533,7 +2492,7 @@
       </c>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2552,7 +2511,7 @@
       </c>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2571,7 +2530,7 @@
       </c>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2590,7 +2549,7 @@
       </c>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2609,7 +2568,7 @@
       </c>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2628,7 +2587,7 @@
       </c>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2647,7 +2606,7 @@
       </c>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2666,7 +2625,7 @@
       </c>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2685,7 +2644,7 @@
       </c>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2704,7 +2663,7 @@
       </c>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2723,7 +2682,7 @@
       </c>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2742,7 +2701,7 @@
       </c>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2761,7 +2720,7 @@
       </c>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2780,7 +2739,7 @@
       </c>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2799,7 +2758,7 @@
       </c>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2818,7 +2777,7 @@
       </c>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2837,7 +2796,7 @@
       </c>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2856,7 +2815,7 @@
       </c>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2875,7 +2834,7 @@
       </c>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2894,7 +2853,7 @@
       </c>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2913,7 +2872,7 @@
       </c>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2932,7 +2891,7 @@
       </c>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2951,7 +2910,7 @@
       </c>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2970,7 +2929,7 @@
       </c>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2989,7 +2948,7 @@
       </c>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -3008,7 +2967,7 @@
       </c>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3027,7 +2986,7 @@
       </c>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3046,7 +3005,7 @@
       </c>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3065,7 +3024,7 @@
       </c>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -3084,7 +3043,7 @@
       </c>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3103,7 +3062,7 @@
       </c>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -3122,7 +3081,7 @@
       </c>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3141,7 +3100,7 @@
       </c>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -3160,7 +3119,7 @@
       </c>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3179,7 +3138,7 @@
       </c>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -3198,7 +3157,7 @@
       </c>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3217,7 +3176,7 @@
       </c>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -3236,7 +3195,7 @@
       </c>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3255,7 +3214,7 @@
       </c>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3274,7 +3233,7 @@
       </c>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3293,7 +3252,7 @@
       </c>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3312,7 +3271,7 @@
       </c>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3331,7 +3290,7 @@
       </c>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3350,7 +3309,7 @@
       </c>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -3369,7 +3328,7 @@
       </c>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3388,7 +3347,7 @@
       </c>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3407,7 +3366,7 @@
       </c>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3426,7 +3385,7 @@
       </c>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3445,7 +3404,7 @@
       </c>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -3464,7 +3423,7 @@
       </c>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -3483,7 +3442,7 @@
       </c>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3502,7 +3461,7 @@
       </c>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -3521,7 +3480,7 @@
       </c>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3540,7 +3499,7 @@
       </c>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3559,7 +3518,7 @@
       </c>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3578,7 +3537,7 @@
       </c>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3597,7 +3556,7 @@
       </c>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3616,7 +3575,7 @@
       </c>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3635,7 +3594,7 @@
       </c>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3654,7 +3613,7 @@
       </c>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3673,7 +3632,7 @@
       </c>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -3692,7 +3651,7 @@
       </c>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3711,7 +3670,7 @@
       </c>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -3730,7 +3689,7 @@
       </c>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3749,7 +3708,7 @@
       </c>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3768,7 +3727,7 @@
       </c>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -3787,7 +3746,7 @@
       </c>
       <c r="K82" s="2"/>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -3806,7 +3765,7 @@
       </c>
       <c r="K83" s="2"/>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -3825,7 +3784,7 @@
       </c>
       <c r="K84" s="2"/>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -3844,7 +3803,7 @@
       </c>
       <c r="K85" s="2"/>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -3863,7 +3822,7 @@
       </c>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -3882,7 +3841,7 @@
       </c>
       <c r="K87" s="2"/>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -3901,7 +3860,7 @@
       </c>
       <c r="K88" s="2"/>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -3920,7 +3879,7 @@
       </c>
       <c r="K89" s="2"/>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -3939,7 +3898,7 @@
       </c>
       <c r="K90" s="2"/>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -3958,7 +3917,7 @@
       </c>
       <c r="K91" s="2"/>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -3977,7 +3936,7 @@
       </c>
       <c r="K92" s="2"/>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -3996,7 +3955,7 @@
       </c>
       <c r="K93" s="2"/>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -4015,7 +3974,7 @@
       </c>
       <c r="K94" s="2"/>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -4034,7 +3993,7 @@
       </c>
       <c r="K95" s="2"/>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -4053,7 +4012,7 @@
       </c>
       <c r="K96" s="2"/>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -4072,7 +4031,7 @@
       </c>
       <c r="K97" s="2"/>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -4091,7 +4050,7 @@
       </c>
       <c r="K98" s="2"/>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4110,7 +4069,7 @@
       </c>
       <c r="K99" s="2"/>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4129,7 +4088,7 @@
       </c>
       <c r="K100" s="2"/>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -4148,7 +4107,7 @@
       </c>
       <c r="K101" s="2"/>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -4167,7 +4126,7 @@
       </c>
       <c r="K102" s="2"/>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4186,7 +4145,7 @@
       </c>
       <c r="K103" s="2"/>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -4205,7 +4164,7 @@
       </c>
       <c r="K104" s="2"/>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -4224,7 +4183,7 @@
       </c>
       <c r="K105" s="2"/>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4243,7 +4202,7 @@
       </c>
       <c r="K106" s="2"/>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4262,7 +4221,7 @@
       </c>
       <c r="K107" s="2"/>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -4281,7 +4240,7 @@
       </c>
       <c r="K108" s="2"/>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -4300,7 +4259,7 @@
       </c>
       <c r="K109" s="2"/>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -4319,7 +4278,7 @@
       </c>
       <c r="K110" s="2"/>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -4338,7 +4297,7 @@
       </c>
       <c r="K111" s="2"/>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -4357,7 +4316,7 @@
       </c>
       <c r="K112" s="2"/>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -4376,7 +4335,7 @@
       </c>
       <c r="K113" s="2"/>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -4395,7 +4354,7 @@
       </c>
       <c r="K114" s="2"/>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -4414,7 +4373,7 @@
       </c>
       <c r="K115" s="2"/>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -4433,7 +4392,7 @@
       </c>
       <c r="K116" s="2"/>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -4452,7 +4411,7 @@
       </c>
       <c r="K117" s="2"/>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -4471,7 +4430,7 @@
       </c>
       <c r="K118" s="2"/>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -4490,7 +4449,7 @@
       </c>
       <c r="K119" s="2"/>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -4509,7 +4468,7 @@
       </c>
       <c r="K120" s="2"/>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -4528,7 +4487,7 @@
       </c>
       <c r="K121" s="2"/>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -4547,7 +4506,7 @@
       </c>
       <c r="K122" s="2"/>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -4566,7 +4525,7 @@
       </c>
       <c r="K123" s="2"/>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -4585,7 +4544,7 @@
       </c>
       <c r="K124" s="2"/>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -4604,7 +4563,7 @@
       </c>
       <c r="K125" s="2"/>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -4623,7 +4582,7 @@
       </c>
       <c r="K126" s="2"/>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -4642,7 +4601,7 @@
       </c>
       <c r="K127" s="2"/>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -4661,7 +4620,7 @@
       </c>
       <c r="K128" s="2"/>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -4680,7 +4639,7 @@
       </c>
       <c r="K129" s="2"/>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -4699,7 +4658,7 @@
       </c>
       <c r="K130" s="2"/>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -4718,7 +4677,7 @@
       </c>
       <c r="K131" s="2"/>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -4737,7 +4696,7 @@
       </c>
       <c r="K132" s="2"/>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -4756,7 +4715,7 @@
       </c>
       <c r="K133" s="2"/>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -4775,7 +4734,7 @@
       </c>
       <c r="K134" s="2"/>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -4794,7 +4753,7 @@
       </c>
       <c r="K135" s="2"/>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -4813,7 +4772,7 @@
       </c>
       <c r="K136" s="2"/>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -4832,7 +4791,7 @@
       </c>
       <c r="K137" s="2"/>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -4851,7 +4810,7 @@
       </c>
       <c r="K138" s="2"/>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -4870,7 +4829,7 @@
       </c>
       <c r="K139" s="2"/>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -4889,7 +4848,7 @@
       </c>
       <c r="K140" s="2"/>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -4908,7 +4867,7 @@
       </c>
       <c r="K141" s="2"/>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -4927,7 +4886,7 @@
       </c>
       <c r="K142" s="2"/>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -4946,7 +4905,7 @@
       </c>
       <c r="K143" s="2"/>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -4965,7 +4924,7 @@
       </c>
       <c r="K144" s="2"/>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -4984,7 +4943,7 @@
       </c>
       <c r="K145" s="2"/>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -5003,7 +4962,7 @@
       </c>
       <c r="K146" s="2"/>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -5022,7 +4981,7 @@
       </c>
       <c r="K147" s="2"/>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -5041,7 +5000,7 @@
       </c>
       <c r="K148" s="2"/>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -5060,7 +5019,7 @@
       </c>
       <c r="K149" s="2"/>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -5079,7 +5038,7 @@
       </c>
       <c r="K150" s="2"/>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -5098,7 +5057,7 @@
       </c>
       <c r="K151" s="2"/>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -5117,7 +5076,7 @@
       </c>
       <c r="K152" s="2"/>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -5136,7 +5095,7 @@
       </c>
       <c r="K153" s="2"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -5155,7 +5114,7 @@
       </c>
       <c r="K154" s="2"/>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -5174,7 +5133,7 @@
       </c>
       <c r="K155" s="2"/>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -5193,7 +5152,7 @@
       </c>
       <c r="K156" s="2"/>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -5212,7 +5171,7 @@
       </c>
       <c r="K157" s="2"/>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -5231,7 +5190,7 @@
       </c>
       <c r="K158" s="2"/>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -5250,7 +5209,7 @@
       </c>
       <c r="K159" s="2"/>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -5269,7 +5228,7 @@
       </c>
       <c r="K160" s="2"/>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -5288,7 +5247,7 @@
       </c>
       <c r="K161" s="2"/>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -5307,7 +5266,7 @@
       </c>
       <c r="K162" s="2"/>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -5326,7 +5285,7 @@
       </c>
       <c r="K163" s="2"/>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -5345,7 +5304,7 @@
       </c>
       <c r="K164" s="2"/>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -5364,7 +5323,7 @@
       </c>
       <c r="K165" s="2"/>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -5383,7 +5342,7 @@
       </c>
       <c r="K166" s="2"/>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -5402,7 +5361,7 @@
       </c>
       <c r="K167" s="2"/>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -5421,7 +5380,7 @@
       </c>
       <c r="K168" s="2"/>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -5440,7 +5399,7 @@
       </c>
       <c r="K169" s="2"/>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -5459,7 +5418,7 @@
       </c>
       <c r="K170" s="2"/>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -5478,7 +5437,7 @@
       </c>
       <c r="K171" s="2"/>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -5497,7 +5456,7 @@
       </c>
       <c r="K172" s="2"/>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -5516,7 +5475,7 @@
       </c>
       <c r="K173" s="2"/>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -5535,7 +5494,7 @@
       </c>
       <c r="K174" s="2"/>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -5554,7 +5513,7 @@
       </c>
       <c r="K175" s="2"/>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -5573,7 +5532,7 @@
       </c>
       <c r="K176" s="2"/>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -5592,7 +5551,7 @@
       </c>
       <c r="K177" s="2"/>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -5611,7 +5570,7 @@
       </c>
       <c r="K178" s="2"/>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -5630,7 +5589,7 @@
       </c>
       <c r="K179" s="2"/>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -5649,7 +5608,7 @@
       </c>
       <c r="K180" s="2"/>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -5668,7 +5627,7 @@
       </c>
       <c r="K181" s="2"/>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -5687,7 +5646,7 @@
       </c>
       <c r="K182" s="2"/>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -5706,7 +5665,7 @@
       </c>
       <c r="K183" s="2"/>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -5725,7 +5684,7 @@
       </c>
       <c r="K184" s="2"/>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -5744,7 +5703,7 @@
       </c>
       <c r="K185" s="2"/>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -5763,7 +5722,7 @@
       </c>
       <c r="K186" s="2"/>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -5782,7 +5741,7 @@
       </c>
       <c r="K187" s="2"/>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -5801,7 +5760,7 @@
       </c>
       <c r="K188" s="2"/>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -5820,7 +5779,7 @@
       </c>
       <c r="K189" s="2"/>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -5839,7 +5798,7 @@
       </c>
       <c r="K190" s="2"/>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -5858,7 +5817,7 @@
       </c>
       <c r="K191" s="2"/>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -5877,7 +5836,7 @@
       </c>
       <c r="K192" s="2"/>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -5896,7 +5855,7 @@
       </c>
       <c r="K193" s="2"/>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -5915,7 +5874,7 @@
       </c>
       <c r="K194" s="2"/>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -5934,7 +5893,7 @@
       </c>
       <c r="K195" s="2"/>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -5953,7 +5912,7 @@
       </c>
       <c r="K196" s="2"/>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -5972,7 +5931,7 @@
       </c>
       <c r="K197" s="2"/>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -5991,7 +5950,7 @@
       </c>
       <c r="K198" s="2"/>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -6010,7 +5969,7 @@
       </c>
       <c r="K199" s="2"/>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -6029,7 +5988,7 @@
       </c>
       <c r="K200" s="2"/>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -6048,7 +6007,7 @@
       </c>
       <c r="K201" s="2"/>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -6067,7 +6026,7 @@
       </c>
       <c r="K202" s="2"/>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -6086,7 +6045,7 @@
       </c>
       <c r="K203" s="2"/>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -6105,7 +6064,7 @@
       </c>
       <c r="K204" s="2"/>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -6124,7 +6083,7 @@
       </c>
       <c r="K205" s="2"/>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -6143,7 +6102,7 @@
       </c>
       <c r="K206" s="2"/>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -6162,7 +6121,7 @@
       </c>
       <c r="K207" s="2"/>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -6181,7 +6140,7 @@
       </c>
       <c r="K208" s="2"/>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -6200,7 +6159,7 @@
       </c>
       <c r="K209" s="2"/>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -6219,7 +6178,7 @@
       </c>
       <c r="K210" s="2"/>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -6238,7 +6197,7 @@
       </c>
       <c r="K211" s="2"/>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -6257,7 +6216,7 @@
       </c>
       <c r="K212" s="2"/>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -6276,7 +6235,7 @@
       </c>
       <c r="K213" s="2"/>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -6295,7 +6254,7 @@
       </c>
       <c r="K214" s="2"/>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -6314,7 +6273,7 @@
       </c>
       <c r="K215" s="2"/>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -6333,7 +6292,7 @@
       </c>
       <c r="K216" s="2"/>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -6352,7 +6311,7 @@
       </c>
       <c r="K217" s="2"/>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -6371,7 +6330,7 @@
       </c>
       <c r="K218" s="2"/>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -6390,7 +6349,7 @@
       </c>
       <c r="K219" s="2"/>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -6409,7 +6368,7 @@
       </c>
       <c r="K220" s="2"/>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -6428,7 +6387,7 @@
       </c>
       <c r="K221" s="2"/>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -6447,7 +6406,7 @@
       </c>
       <c r="K222" s="2"/>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -6466,7 +6425,7 @@
       </c>
       <c r="K223" s="2"/>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -6485,7 +6444,7 @@
       </c>
       <c r="K224" s="2"/>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -6504,7 +6463,7 @@
       </c>
       <c r="K225" s="2"/>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -6523,7 +6482,7 @@
       </c>
       <c r="K226" s="2"/>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -6542,7 +6501,7 @@
       </c>
       <c r="K227" s="2"/>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -6561,7 +6520,7 @@
       </c>
       <c r="K228" s="2"/>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -6580,7 +6539,7 @@
       </c>
       <c r="K229" s="2"/>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -6599,7 +6558,7 @@
       </c>
       <c r="K230" s="2"/>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -6618,7 +6577,7 @@
       </c>
       <c r="K231" s="2"/>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -6637,7 +6596,7 @@
       </c>
       <c r="K232" s="2"/>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -6656,7 +6615,7 @@
       </c>
       <c r="K233" s="2"/>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -6675,7 +6634,7 @@
       </c>
       <c r="K234" s="2"/>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -6694,7 +6653,7 @@
       </c>
       <c r="K235" s="2"/>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -6713,7 +6672,7 @@
       </c>
       <c r="K236" s="2"/>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -6732,7 +6691,7 @@
       </c>
       <c r="K237" s="2"/>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -6751,7 +6710,7 @@
       </c>
       <c r="K238" s="2"/>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -6770,7 +6729,7 @@
       </c>
       <c r="K239" s="2"/>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -6789,7 +6748,7 @@
       </c>
       <c r="K240" s="2"/>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -6808,7 +6767,7 @@
       </c>
       <c r="K241" s="2"/>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -6827,7 +6786,7 @@
       </c>
       <c r="K242" s="2"/>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -6846,7 +6805,7 @@
       </c>
       <c r="K243" s="2"/>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -6865,7 +6824,7 @@
       </c>
       <c r="K244" s="2"/>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -6884,7 +6843,7 @@
       </c>
       <c r="K245" s="2"/>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -6903,7 +6862,7 @@
       </c>
       <c r="K246" s="2"/>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -6922,7 +6881,7 @@
       </c>
       <c r="K247" s="2"/>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -6941,7 +6900,7 @@
       </c>
       <c r="K248" s="2"/>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -6960,7 +6919,7 @@
       </c>
       <c r="K249" s="2"/>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -6979,7 +6938,7 @@
       </c>
       <c r="K250" s="2"/>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -6998,7 +6957,7 @@
       </c>
       <c r="K251" s="2"/>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -7017,7 +6976,7 @@
       </c>
       <c r="K252" s="2"/>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -7036,7 +6995,7 @@
       </c>
       <c r="K253" s="2"/>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -7055,7 +7014,7 @@
       </c>
       <c r="K254" s="2"/>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -7074,7 +7033,7 @@
       </c>
       <c r="K255" s="2"/>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -7093,7 +7052,7 @@
       </c>
       <c r="K256" s="2"/>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -7112,7 +7071,7 @@
       </c>
       <c r="K257" s="2"/>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -7131,7 +7090,7 @@
       </c>
       <c r="K258" s="2"/>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -7150,7 +7109,7 @@
       </c>
       <c r="K259" s="2"/>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -7169,7 +7128,7 @@
       </c>
       <c r="K260" s="2"/>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -7188,7 +7147,7 @@
       </c>
       <c r="K261" s="2"/>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -7207,7 +7166,7 @@
       </c>
       <c r="K262" s="2"/>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -7226,7 +7185,7 @@
       </c>
       <c r="K263" s="2"/>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -7245,7 +7204,7 @@
       </c>
       <c r="K264" s="2"/>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -7264,7 +7223,7 @@
       </c>
       <c r="K265" s="2"/>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -7283,7 +7242,7 @@
       </c>
       <c r="K266" s="2"/>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -7302,7 +7261,7 @@
       </c>
       <c r="K267" s="2"/>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -7321,7 +7280,7 @@
       </c>
       <c r="K268" s="2"/>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -7340,7 +7299,7 @@
       </c>
       <c r="K269" s="2"/>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -7359,7 +7318,7 @@
       </c>
       <c r="K270" s="2"/>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -7378,7 +7337,7 @@
       </c>
       <c r="K271" s="2"/>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -7397,7 +7356,7 @@
       </c>
       <c r="K272" s="2"/>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -7416,7 +7375,7 @@
       </c>
       <c r="K273" s="2"/>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -7435,7 +7394,7 @@
       </c>
       <c r="K274" s="2"/>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -7454,7 +7413,7 @@
       </c>
       <c r="K275" s="2"/>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -7473,7 +7432,7 @@
       </c>
       <c r="K276" s="2"/>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -7492,7 +7451,7 @@
       </c>
       <c r="K277" s="2"/>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -7511,7 +7470,7 @@
       </c>
       <c r="K278" s="2"/>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -7530,7 +7489,7 @@
       </c>
       <c r="K279" s="2"/>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -7549,7 +7508,7 @@
       </c>
       <c r="K280" s="2"/>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -7568,7 +7527,7 @@
       </c>
       <c r="K281" s="2"/>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -7587,7 +7546,7 @@
       </c>
       <c r="K282" s="2"/>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -7606,7 +7565,7 @@
       </c>
       <c r="K283" s="2"/>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -7625,7 +7584,7 @@
       </c>
       <c r="K284" s="2"/>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -7644,7 +7603,7 @@
       </c>
       <c r="K285" s="2"/>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -7663,7 +7622,7 @@
       </c>
       <c r="K286" s="2"/>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -7682,7 +7641,7 @@
       </c>
       <c r="K287" s="2"/>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -7701,7 +7660,7 @@
       </c>
       <c r="K288" s="2"/>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -7720,7 +7679,7 @@
       </c>
       <c r="K289" s="2"/>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -7739,7 +7698,7 @@
       </c>
       <c r="K290" s="2"/>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -7758,7 +7717,7 @@
       </c>
       <c r="K291" s="2"/>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -7777,7 +7736,7 @@
       </c>
       <c r="K292" s="2"/>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -7796,7 +7755,7 @@
       </c>
       <c r="K293" s="2"/>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -7815,7 +7774,7 @@
       </c>
       <c r="K294" s="2"/>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -7834,7 +7793,7 @@
       </c>
       <c r="K295" s="2"/>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -7853,7 +7812,7 @@
       </c>
       <c r="K296" s="2"/>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -7872,7 +7831,7 @@
       </c>
       <c r="K297" s="2"/>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -7891,7 +7850,7 @@
       </c>
       <c r="K298" s="2"/>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -7910,7 +7869,7 @@
       </c>
       <c r="K299" s="2"/>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -7929,7 +7888,7 @@
       </c>
       <c r="K300" s="2"/>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -7948,7 +7907,7 @@
       </c>
       <c r="K301" s="2"/>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -7967,7 +7926,7 @@
       </c>
       <c r="K302" s="2"/>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -7986,7 +7945,7 @@
       </c>
       <c r="K303" s="2"/>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -8005,7 +7964,7 @@
       </c>
       <c r="K304" s="2"/>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -8024,7 +7983,7 @@
       </c>
       <c r="K305" s="2"/>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -8043,7 +8002,7 @@
       </c>
       <c r="K306" s="2"/>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -8062,7 +8021,7 @@
       </c>
       <c r="K307" s="2"/>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -8081,7 +8040,7 @@
       </c>
       <c r="K308" s="2"/>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -8100,7 +8059,7 @@
       </c>
       <c r="K309" s="2"/>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -8119,7 +8078,7 @@
       </c>
       <c r="K310" s="2"/>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -8138,7 +8097,7 @@
       </c>
       <c r="K311" s="2"/>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -8157,7 +8116,7 @@
       </c>
       <c r="K312" s="2"/>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -8176,7 +8135,7 @@
       </c>
       <c r="K313" s="2"/>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -8195,7 +8154,7 @@
       </c>
       <c r="K314" s="2"/>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -8214,7 +8173,7 @@
       </c>
       <c r="K315" s="2"/>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -8233,7 +8192,7 @@
       </c>
       <c r="K316" s="2"/>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -8252,7 +8211,7 @@
       </c>
       <c r="K317" s="2"/>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -8271,7 +8230,7 @@
       </c>
       <c r="K318" s="2"/>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -8290,7 +8249,7 @@
       </c>
       <c r="K319" s="2"/>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -8309,7 +8268,7 @@
       </c>
       <c r="K320" s="2"/>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -8328,7 +8287,7 @@
       </c>
       <c r="K321" s="2"/>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
@@ -8347,7 +8306,7 @@
       </c>
       <c r="K322" s="2"/>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
@@ -8366,7 +8325,7 @@
       </c>
       <c r="K323" s="2"/>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
@@ -8385,7 +8344,7 @@
       </c>
       <c r="K324" s="2"/>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
@@ -8404,7 +8363,7 @@
       </c>
       <c r="K325" s="2"/>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
@@ -8423,7 +8382,7 @@
       </c>
       <c r="K326" s="2"/>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
@@ -8442,7 +8401,7 @@
       </c>
       <c r="K327" s="2"/>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
@@ -8461,7 +8420,7 @@
       </c>
       <c r="K328" s="2"/>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
@@ -8480,7 +8439,7 @@
       </c>
       <c r="K329" s="2"/>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
@@ -8499,7 +8458,7 @@
       </c>
       <c r="K330" s="2"/>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -8518,7 +8477,7 @@
       </c>
       <c r="K331" s="2"/>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
@@ -8537,7 +8496,7 @@
       </c>
       <c r="K332" s="2"/>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
@@ -8556,7 +8515,7 @@
       </c>
       <c r="K333" s="2"/>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
@@ -8575,7 +8534,7 @@
       </c>
       <c r="K334" s="2"/>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
@@ -8594,7 +8553,7 @@
       </c>
       <c r="K335" s="2"/>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
@@ -8613,7 +8572,7 @@
       </c>
       <c r="K336" s="2"/>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
@@ -8632,7 +8591,7 @@
       </c>
       <c r="K337" s="2"/>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
@@ -8651,7 +8610,7 @@
       </c>
       <c r="K338" s="2"/>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
@@ -8670,7 +8629,7 @@
       </c>
       <c r="K339" s="2"/>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
@@ -8689,7 +8648,7 @@
       </c>
       <c r="K340" s="2"/>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
@@ -8708,7 +8667,7 @@
       </c>
       <c r="K341" s="2"/>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
@@ -8727,7 +8686,7 @@
       </c>
       <c r="K342" s="2"/>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
@@ -8746,7 +8705,7 @@
       </c>
       <c r="K343" s="2"/>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
@@ -8765,7 +8724,7 @@
       </c>
       <c r="K344" s="2"/>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
@@ -8784,7 +8743,7 @@
       </c>
       <c r="K345" s="2"/>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
@@ -8803,7 +8762,7 @@
       </c>
       <c r="K346" s="2"/>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
@@ -8822,7 +8781,7 @@
       </c>
       <c r="K347" s="2"/>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
@@ -8841,7 +8800,7 @@
       </c>
       <c r="K348" s="2"/>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
@@ -8860,7 +8819,7 @@
       </c>
       <c r="K349" s="2"/>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
@@ -8879,7 +8838,7 @@
       </c>
       <c r="K350" s="2"/>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
@@ -8898,7 +8857,7 @@
       </c>
       <c r="K351" s="2"/>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
@@ -8917,7 +8876,7 @@
       </c>
       <c r="K352" s="2"/>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
@@ -8936,7 +8895,7 @@
       </c>
       <c r="K353" s="2"/>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2"/>
@@ -8955,7 +8914,7 @@
       </c>
       <c r="K354" s="2"/>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
@@ -8974,7 +8933,7 @@
       </c>
       <c r="K355" s="2"/>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
@@ -8993,7 +8952,7 @@
       </c>
       <c r="K356" s="2"/>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
@@ -9012,7 +8971,7 @@
       </c>
       <c r="K357" s="2"/>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
@@ -9031,7 +8990,7 @@
       </c>
       <c r="K358" s="2"/>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
@@ -9050,7 +9009,7 @@
       </c>
       <c r="K359" s="2"/>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
@@ -9069,7 +9028,7 @@
       </c>
       <c r="K360" s="2"/>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
@@ -9088,7 +9047,7 @@
       </c>
       <c r="K361" s="2"/>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
@@ -9107,7 +9066,7 @@
       </c>
       <c r="K362" s="2"/>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
@@ -9126,7 +9085,7 @@
       </c>
       <c r="K363" s="2"/>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
@@ -9145,7 +9104,7 @@
       </c>
       <c r="K364" s="2"/>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
@@ -9164,7 +9123,7 @@
       </c>
       <c r="K365" s="2"/>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -9183,7 +9142,7 @@
       </c>
       <c r="K366" s="2"/>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
@@ -9202,7 +9161,7 @@
       </c>
       <c r="K367" s="2"/>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
@@ -9221,7 +9180,7 @@
       </c>
       <c r="K368" s="2"/>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
@@ -9240,7 +9199,7 @@
       </c>
       <c r="K369" s="2"/>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
@@ -9259,7 +9218,7 @@
       </c>
       <c r="K370" s="2"/>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
@@ -9278,7 +9237,7 @@
       </c>
       <c r="K371" s="2"/>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
@@ -9297,7 +9256,7 @@
       </c>
       <c r="K372" s="2"/>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
@@ -9316,7 +9275,7 @@
       </c>
       <c r="K373" s="2"/>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
@@ -9335,7 +9294,7 @@
       </c>
       <c r="K374" s="2"/>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
@@ -9354,7 +9313,7 @@
       </c>
       <c r="K375" s="2"/>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
@@ -9373,7 +9332,7 @@
       </c>
       <c r="K376" s="2"/>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
@@ -9392,7 +9351,7 @@
       </c>
       <c r="K377" s="2"/>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
@@ -9411,7 +9370,7 @@
       </c>
       <c r="K378" s="2"/>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
@@ -9430,7 +9389,7 @@
       </c>
       <c r="K379" s="2"/>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
@@ -9449,7 +9408,7 @@
       </c>
       <c r="K380" s="2"/>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
@@ -9468,7 +9427,7 @@
       </c>
       <c r="K381" s="2"/>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
@@ -9487,7 +9446,7 @@
       </c>
       <c r="K382" s="2"/>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
@@ -9506,7 +9465,7 @@
       </c>
       <c r="K383" s="2"/>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
@@ -9525,7 +9484,7 @@
       </c>
       <c r="K384" s="2"/>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -9544,7 +9503,7 @@
       </c>
       <c r="K385" s="2"/>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
@@ -9563,7 +9522,7 @@
       </c>
       <c r="K386" s="2"/>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
@@ -9582,7 +9541,7 @@
       </c>
       <c r="K387" s="2"/>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
@@ -9601,7 +9560,7 @@
       </c>
       <c r="K388" s="2"/>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
@@ -9620,7 +9579,7 @@
       </c>
       <c r="K389" s="2"/>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
@@ -9639,7 +9598,7 @@
       </c>
       <c r="K390" s="2"/>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
@@ -9658,7 +9617,7 @@
       </c>
       <c r="K391" s="2"/>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
@@ -9677,7 +9636,7 @@
       </c>
       <c r="K392" s="2"/>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
@@ -9696,7 +9655,7 @@
       </c>
       <c r="K393" s="2"/>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
@@ -9715,7 +9674,7 @@
       </c>
       <c r="K394" s="2"/>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
@@ -9734,7 +9693,7 @@
       </c>
       <c r="K395" s="2"/>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
@@ -9753,7 +9712,7 @@
       </c>
       <c r="K396" s="2"/>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
@@ -9772,7 +9731,7 @@
       </c>
       <c r="K397" s="2"/>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
@@ -9791,7 +9750,7 @@
       </c>
       <c r="K398" s="2"/>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
@@ -9810,7 +9769,7 @@
       </c>
       <c r="K399" s="2"/>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
@@ -9829,7 +9788,7 @@
       </c>
       <c r="K400" s="2"/>
     </row>
-    <row r="401" spans="1:11">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
@@ -9848,7 +9807,7 @@
       </c>
       <c r="K401" s="2"/>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
@@ -9867,7 +9826,7 @@
       </c>
       <c r="K402" s="2"/>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
@@ -9886,7 +9845,7 @@
       </c>
       <c r="K403" s="2"/>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
@@ -9905,7 +9864,7 @@
       </c>
       <c r="K404" s="2"/>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
@@ -9924,7 +9883,7 @@
       </c>
       <c r="K405" s="2"/>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
@@ -9943,7 +9902,7 @@
       </c>
       <c r="K406" s="2"/>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="2"/>
@@ -9962,7 +9921,7 @@
       </c>
       <c r="K407" s="2"/>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
@@ -9981,7 +9940,7 @@
       </c>
       <c r="K408" s="2"/>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
@@ -10000,7 +9959,7 @@
       </c>
       <c r="K409" s="2"/>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
@@ -10019,7 +9978,7 @@
       </c>
       <c r="K410" s="2"/>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
@@ -10038,7 +9997,7 @@
       </c>
       <c r="K411" s="2"/>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
@@ -10057,7 +10016,7 @@
       </c>
       <c r="K412" s="2"/>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
@@ -10076,7 +10035,7 @@
       </c>
       <c r="K413" s="2"/>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="2"/>
@@ -10095,7 +10054,7 @@
       </c>
       <c r="K414" s="2"/>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
@@ -10114,7 +10073,7 @@
       </c>
       <c r="K415" s="2"/>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
@@ -10133,7 +10092,7 @@
       </c>
       <c r="K416" s="2"/>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
@@ -10152,7 +10111,7 @@
       </c>
       <c r="K417" s="2"/>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
@@ -10171,7 +10130,7 @@
       </c>
       <c r="K418" s="2"/>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
@@ -10190,7 +10149,7 @@
       </c>
       <c r="K419" s="2"/>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
@@ -10209,7 +10168,7 @@
       </c>
       <c r="K420" s="2"/>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
@@ -10228,7 +10187,7 @@
       </c>
       <c r="K421" s="2"/>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
@@ -10247,7 +10206,7 @@
       </c>
       <c r="K422" s="2"/>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
@@ -10266,7 +10225,7 @@
       </c>
       <c r="K423" s="2"/>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
@@ -10285,7 +10244,7 @@
       </c>
       <c r="K424" s="2"/>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
@@ -10304,7 +10263,7 @@
       </c>
       <c r="K425" s="2"/>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="2"/>
@@ -10323,7 +10282,7 @@
       </c>
       <c r="K426" s="2"/>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
@@ -10342,7 +10301,7 @@
       </c>
       <c r="K427" s="2"/>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
@@ -10361,7 +10320,7 @@
       </c>
       <c r="K428" s="2"/>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="2"/>
@@ -10380,7 +10339,7 @@
       </c>
       <c r="K429" s="2"/>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -10399,7 +10358,7 @@
       </c>
       <c r="K430" s="2"/>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
@@ -10418,7 +10377,7 @@
       </c>
       <c r="K431" s="2"/>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="2"/>
@@ -10437,7 +10396,7 @@
       </c>
       <c r="K432" s="2"/>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
@@ -10456,7 +10415,7 @@
       </c>
       <c r="K433" s="2"/>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
@@ -10475,7 +10434,7 @@
       </c>
       <c r="K434" s="2"/>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -10494,7 +10453,7 @@
       </c>
       <c r="K435" s="2"/>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
@@ -10513,7 +10472,7 @@
       </c>
       <c r="K436" s="2"/>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="2"/>
@@ -10532,7 +10491,7 @@
       </c>
       <c r="K437" s="2"/>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
@@ -10551,7 +10510,7 @@
       </c>
       <c r="K438" s="2"/>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
@@ -10570,7 +10529,7 @@
       </c>
       <c r="K439" s="2"/>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
@@ -10589,7 +10548,7 @@
       </c>
       <c r="K440" s="2"/>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -10608,7 +10567,7 @@
       </c>
       <c r="K441" s="2"/>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
@@ -10627,7 +10586,7 @@
       </c>
       <c r="K442" s="2"/>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="2"/>
@@ -10646,7 +10605,7 @@
       </c>
       <c r="K443" s="2"/>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
@@ -10665,7 +10624,7 @@
       </c>
       <c r="K444" s="2"/>
     </row>
-    <row r="445" spans="1:11">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
@@ -10684,7 +10643,7 @@
       </c>
       <c r="K445" s="2"/>
     </row>
-    <row r="446" spans="1:11">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
@@ -10703,7 +10662,7 @@
       </c>
       <c r="K446" s="2"/>
     </row>
-    <row r="447" spans="1:11">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
@@ -10722,7 +10681,7 @@
       </c>
       <c r="K447" s="2"/>
     </row>
-    <row r="448" spans="1:11">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
@@ -10741,7 +10700,7 @@
       </c>
       <c r="K448" s="2"/>
     </row>
-    <row r="449" spans="1:11">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="2"/>
@@ -10760,7 +10719,7 @@
       </c>
       <c r="K449" s="2"/>
     </row>
-    <row r="450" spans="1:11">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
@@ -10779,7 +10738,7 @@
       </c>
       <c r="K450" s="2"/>
     </row>
-    <row r="451" spans="1:11">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
@@ -10798,7 +10757,7 @@
       </c>
       <c r="K451" s="2"/>
     </row>
-    <row r="452" spans="1:11">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
@@ -10817,7 +10776,7 @@
       </c>
       <c r="K452" s="2"/>
     </row>
-    <row r="453" spans="1:11">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
@@ -10836,7 +10795,7 @@
       </c>
       <c r="K453" s="2"/>
     </row>
-    <row r="454" spans="1:11">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
@@ -10855,7 +10814,7 @@
       </c>
       <c r="K454" s="2"/>
     </row>
-    <row r="455" spans="1:11">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="2"/>
@@ -10874,7 +10833,7 @@
       </c>
       <c r="K455" s="2"/>
     </row>
-    <row r="456" spans="1:11">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
@@ -10893,7 +10852,7 @@
       </c>
       <c r="K456" s="2"/>
     </row>
-    <row r="457" spans="1:11">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
@@ -10912,7 +10871,7 @@
       </c>
       <c r="K457" s="2"/>
     </row>
-    <row r="458" spans="1:11">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
@@ -10931,7 +10890,7 @@
       </c>
       <c r="K458" s="2"/>
     </row>
-    <row r="459" spans="1:11">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
@@ -10950,7 +10909,7 @@
       </c>
       <c r="K459" s="2"/>
     </row>
-    <row r="460" spans="1:11">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
@@ -10969,7 +10928,7 @@
       </c>
       <c r="K460" s="2"/>
     </row>
-    <row r="461" spans="1:11">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="2"/>
@@ -10988,7 +10947,7 @@
       </c>
       <c r="K461" s="2"/>
     </row>
-    <row r="462" spans="1:11">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
@@ -11007,7 +10966,7 @@
       </c>
       <c r="K462" s="2"/>
     </row>
-    <row r="463" spans="1:11">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
@@ -11026,7 +10985,7 @@
       </c>
       <c r="K463" s="2"/>
     </row>
-    <row r="464" spans="1:11">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="2"/>
@@ -11045,7 +11004,7 @@
       </c>
       <c r="K464" s="2"/>
     </row>
-    <row r="465" spans="1:11">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
@@ -11064,7 +11023,7 @@
       </c>
       <c r="K465" s="2"/>
     </row>
-    <row r="466" spans="1:11">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="2"/>
@@ -11083,7 +11042,7 @@
       </c>
       <c r="K466" s="2"/>
     </row>
-    <row r="467" spans="1:11">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
@@ -11102,7 +11061,7 @@
       </c>
       <c r="K467" s="2"/>
     </row>
-    <row r="468" spans="1:11">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="2"/>
@@ -11121,7 +11080,7 @@
       </c>
       <c r="K468" s="2"/>
     </row>
-    <row r="469" spans="1:11">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
@@ -11140,7 +11099,7 @@
       </c>
       <c r="K469" s="2"/>
     </row>
-    <row r="470" spans="1:11">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="2"/>
@@ -11159,7 +11118,7 @@
       </c>
       <c r="K470" s="2"/>
     </row>
-    <row r="471" spans="1:11">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
@@ -11178,7 +11137,7 @@
       </c>
       <c r="K471" s="2"/>
     </row>
-    <row r="472" spans="1:11">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
@@ -11197,7 +11156,7 @@
       </c>
       <c r="K472" s="2"/>
     </row>
-    <row r="473" spans="1:11">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="2"/>
@@ -11216,7 +11175,7 @@
       </c>
       <c r="K473" s="2"/>
     </row>
-    <row r="474" spans="1:11">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
@@ -11235,7 +11194,7 @@
       </c>
       <c r="K474" s="2"/>
     </row>
-    <row r="475" spans="1:11">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
@@ -11254,7 +11213,7 @@
       </c>
       <c r="K475" s="2"/>
     </row>
-    <row r="476" spans="1:11">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
@@ -11273,7 +11232,7 @@
       </c>
       <c r="K476" s="2"/>
     </row>
-    <row r="477" spans="1:11">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
@@ -11292,7 +11251,7 @@
       </c>
       <c r="K477" s="2"/>
     </row>
-    <row r="478" spans="1:11">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
@@ -11311,7 +11270,7 @@
       </c>
       <c r="K478" s="2"/>
     </row>
-    <row r="479" spans="1:11">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
@@ -11330,7 +11289,7 @@
       </c>
       <c r="K479" s="2"/>
     </row>
-    <row r="480" spans="1:11">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
@@ -11349,7 +11308,7 @@
       </c>
       <c r="K480" s="2"/>
     </row>
-    <row r="481" spans="1:11">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
@@ -11368,7 +11327,7 @@
       </c>
       <c r="K481" s="2"/>
     </row>
-    <row r="482" spans="1:11">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="2"/>
@@ -11387,7 +11346,7 @@
       </c>
       <c r="K482" s="2"/>
     </row>
-    <row r="483" spans="1:11">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
@@ -11406,7 +11365,7 @@
       </c>
       <c r="K483" s="2"/>
     </row>
-    <row r="484" spans="1:11">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
@@ -11425,7 +11384,7 @@
       </c>
       <c r="K484" s="2"/>
     </row>
-    <row r="485" spans="1:11">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
@@ -11444,7 +11403,7 @@
       </c>
       <c r="K485" s="2"/>
     </row>
-    <row r="486" spans="1:11">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
@@ -11463,7 +11422,7 @@
       </c>
       <c r="K486" s="2"/>
     </row>
-    <row r="487" spans="1:11">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
@@ -11482,7 +11441,7 @@
       </c>
       <c r="K487" s="2"/>
     </row>
-    <row r="488" spans="1:11">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="2"/>
@@ -11501,7 +11460,7 @@
       </c>
       <c r="K488" s="2"/>
     </row>
-    <row r="489" spans="1:11">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
@@ -11520,7 +11479,7 @@
       </c>
       <c r="K489" s="2"/>
     </row>
-    <row r="490" spans="1:11">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
@@ -11539,7 +11498,7 @@
       </c>
       <c r="K490" s="2"/>
     </row>
-    <row r="491" spans="1:11">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
@@ -11558,7 +11517,7 @@
       </c>
       <c r="K491" s="2"/>
     </row>
-    <row r="492" spans="1:11">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
@@ -11577,7 +11536,7 @@
       </c>
       <c r="K492" s="2"/>
     </row>
-    <row r="493" spans="1:11">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
@@ -11596,7 +11555,7 @@
       </c>
       <c r="K493" s="2"/>
     </row>
-    <row r="494" spans="1:11">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="2"/>
@@ -11615,7 +11574,7 @@
       </c>
       <c r="K494" s="2"/>
     </row>
-    <row r="495" spans="1:11">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
@@ -11634,7 +11593,7 @@
       </c>
       <c r="K495" s="2"/>
     </row>
-    <row r="496" spans="1:11">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
@@ -11653,7 +11612,7 @@
       </c>
       <c r="K496" s="2"/>
     </row>
-    <row r="497" spans="1:11">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
@@ -11672,7 +11631,7 @@
       </c>
       <c r="K497" s="2"/>
     </row>
-    <row r="498" spans="1:11">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
@@ -11691,7 +11650,7 @@
       </c>
       <c r="K498" s="2"/>
     </row>
-    <row r="499" spans="1:11">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
@@ -11710,7 +11669,7 @@
       </c>
       <c r="K499" s="2"/>
     </row>
-    <row r="500" spans="1:11">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
@@ -11729,7 +11688,7 @@
       </c>
       <c r="K500" s="2"/>
     </row>
-    <row r="501" spans="1:11">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="2"/>
@@ -11762,28 +11721,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="16" customWidth="1"/>
+    <col min="1" max="4" width="16.0078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2">
@@ -11795,9 +11754,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2">
@@ -11809,9 +11768,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2">
@@ -11823,9 +11782,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2">
@@ -11837,9 +11796,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -11851,9 +11810,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
@@ -11865,9 +11824,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -11879,9 +11838,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2">
@@ -11893,9 +11852,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
@@ -11907,9 +11866,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2">
@@ -11921,9 +11880,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2">
@@ -11935,9 +11894,9 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2">
@@ -11949,15 +11908,15 @@
         <v>-4167</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B15" s="3">
         <f>SUM(B2:B13)</f>
@@ -11981,29 +11940,29 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="6" width="22" customWidth="1"/>
+    <col min="1" max="6" width="22.05859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -12020,96 +11979,96 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="1" max="1" width="29.99609375" customWidth="1"/>
+    <col min="2" max="2" width="23.9453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21">
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B2" s="7">
         <f>Paramètres!B6</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B3" s="7">
         <f>SUM('CA mensuel'!B2:B13)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B4" s="7">
         <f>B2-B3</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B5" s="7">
         <f>COUNTA(Clients!A2:A500)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B6" s="7">
         <f>COUNTA(Devis!A2:A500)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B7" s="7">
         <f>COUNTIF(Devis!K2:K500,"Accepté")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B8" s="8">
         <f>IF(B6=0,0,B7/B6)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B9" s="7">
         <f>SUM(Frais!D2:D1000)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="54.75">
+    <row r="11" spans="1:2" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>120</v>
+        <v>66</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Wagnon_Paysage_Outil_Patron_V9.xlsx
+++ b/Wagnon_Paysage_Outil_Patron_V9.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{2BCE9CAD-350C-7B4A-A9D8-4371C2F628A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" windowHeight="0" windowWidth="0" xWindow="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="0"/>
   </bookViews>
   <sheets>
     <sheet name="Mode Chantier V9" sheetId="1" r:id="rId1"/>
@@ -440,60 +440,89 @@
   <si>
     <t>07 84 31 26 42</t>
   </si>
+  <si>
+    <t>À faire,Devis envoyé,Accepté,Refusé,Terminé,À relancer</t>
+  </si>
+  <si>
+    <t>Brouillon,Envoyé,Accepté,Refusé,Terminé</t>
+  </si>
+  <si>
+    <t>Carburant,Duster,Assurance,Remorque,Déchèterie,Matériel,Communication,Téléphone,Comptabilité,Autre</t>
+  </si>
+  <si>
+    <t>Accepté</t>
+  </si>
+  <si>
+    <t>En attente,Accepté,Refusé</t>
+  </si>
+  <si>
+    <t>Wagnon Titou</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" count="1" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="9">
+    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);(&quot;$&quot;#,##0)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red](&quot;$&quot;#,##0)"/>
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);(&quot;$&quot;#,##0.00)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red](&quot;$&quot;#,##0.00)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* (#,##0.00);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* (#,##0.00);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b/>
+      <color rgb="FF2F6B3F"/>
       <sz val="14"/>
-      <color rgb="FF2F6B3F"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="20"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b/>
+      <color rgb="FF000000"/>
       <sz val="14"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b/>
+      <color rgb="FF000000"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -531,15 +560,25 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal style="none">
+        <color rgb="FF000000"/>
+      </diagonal>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -580,7 +619,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,7 +638,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
   <c:roundedCorners val="1"/>
@@ -1243,16 +1282,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.98046875" customWidth="1"/>
     <col min="2" max="2" width="23.9453125" customWidth="1"/>
     <col min="3" max="4" width="22.05859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.5" x14ac:dyDescent="0.35">
+    <row ht="25.5" r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1265,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1324,7 +1362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row ht="18.75" r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>10</v>
       </c>
@@ -1337,7 +1375,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+    <row ht="18" r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1346,7 +1384,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
+    <row ht="18.75" r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>13</v>
       </c>
@@ -1380,9 +1418,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.98046875" customWidth="1"/>
     <col min="2" max="2" width="25.01953125" customWidth="1"/>
@@ -1440,7 +1477,7 @@
       <c r="A8" t="s">
         <v>119</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <f>ROUND((B3*Paramètres!B2+B4*Paramètres!B3+B5+B6)*(1+Paramètres!B4/100)/5,0)*5</f>
         <v>95</v>
       </c>
@@ -1449,9 +1486,9 @@
       <c r="A9" t="s">
         <v>120</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <f>IF(B2=0,0,B8/B2)</f>
-        <v>0.15833333333333333</v>
+        <v>0.158333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1460,9 +1497,8 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.015625" customWidth="1"/>
     <col min="2" max="2" width="25.01953125" customWidth="1"/>
@@ -1512,7 +1548,7 @@
       <c r="A7" t="s">
         <v>119</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <f>ROUND((B3*Paramètres!B2+B4*Paramètres!B3+B5)*(1+Paramètres!B4/100)/5,0)*5</f>
         <v>210</v>
       </c>
@@ -1521,7 +1557,7 @@
       <c r="A8" t="s">
         <v>120</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <f>IF(B2=0,0,B7/B2)</f>
         <v>0.42</v>
       </c>
@@ -1532,9 +1568,8 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.99609375" customWidth="1"/>
     <col min="2" max="2" width="25.01953125" customWidth="1"/>
@@ -1584,7 +1619,7 @@
       <c r="A7" t="s">
         <v>119</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <f>ROUND((B2*(1+Paramètres!B5/100)+B3*Paramètres!B2+B4*Paramètres!B3+B5)*(1+Paramètres!B4/100)/5,0)*5</f>
         <v>605</v>
       </c>
@@ -1595,9 +1630,8 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.98046875" customWidth="1"/>
     <col min="2" max="2" width="34.03125" customWidth="1"/>
@@ -1625,9 +1659,8 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
@@ -1648,7 +1681,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E72 E73 E74 E75 E76 E77 E78 E79 E80 E81 E82 E83 E84 E85 E86 E87 E88 E89 E90 E91 E92 E93 E94 E95 E96 E97 E98 E99 E100 E101 E102 E103 E104 E105 E106 E107 E108 E109 E110 E111 E112 E113 E114 E115 E116 E117 E118 E119 E120 E121 E122 E123 E124 E125 E126 E127 E128 E129 E130 E131 E132 E133 E134 E135 E136 E137 E138 E139 E140 E141 E142 E143 E144 E145 E146 E147 E148 E149 E150 E151 E152 E153 E154 E155 E156 E157 E158 E159 E160 E161 E162 E163 E164 E165 E166 E167 E168 E169 E170 E171 E172 E173 E174 E175 E176 E177 E178 E179 E180 E181 E182 E183 E184 E185 E186 E187 E188 E189 E190 E191 E192 E193 E194 E195 E196 E197 E198 E199 E200 E201 E202 E203 E204 E205 E206 E207 E208 E209 E210 E211 E212 E213 E214 E215 E216 E217 E218 E219 E220 E221 E222 E223 E224 E225 E226 E227 E228 E229 E230 E231 E232 E233 E234 E235 E236 E237 E238 E239 E240 E241 E242 E243 E244 E245 E246 E247 E248 E249 E250 E251 E252 E253 E254 E255 E256 E257 E258 E259 E260 E261 E262 E263 E264 E265 E266 E267 E268 E269 E270 E271 E272 E273 E274 E275 E276 E277 E278 E279 E280 E281 E282 E283 E284 E285 E286 E287 E288 E289 E290 E291 E292 E293 E294 E295 E296 E297 E298 E299 E300 E301" xr:uid="{00000000-0002-0000-0D00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E72 E73 E74 E75 E76 E77 E78 E79 E80 E81 E82 E83 E84 E85 E86 E87 E88 E89 E90 E91 E92 E93 E94 E95 E96 E97 E98 E99 E100 E101 E102 E103 E104 E105 E106 E107 E108 E109 E110 E111 E112 E113 E114 E115 E116 E117 E118 E119 E120 E121 E122 E123 E124 E125 E126 E127 E128 E129 E130 E131 E132 E133 E134 E135 E136 E137 E138 E139 E140 E141 E142 E143 E144 E145 E146 E147 E148 E149 E150 E151 E152 E153 E154 E155 E156 E157 E158 E159 E160 E161 E162 E163 E164 E165 E166 E167 E168 E169 E170 E171 E172 E173 E174 E175 E176 E177 E178 E179 E180 E181 E182 E183 E184 E185 E186 E187 E188 E189 E190 E191 E192 E193 E194 E195 E196 E197 E198 E199 E200 E201 E202 E203 E204 E205 E206 E207 E208 E209 E210 E211 E212 E213 E214 E215 E216 E217 E218 E219 E220 E221 E222 E223 E224 E225 E226 E227 E228 E229 E230 E231 E232 E233 E234 E235 E236 E237 E238 E239 E240 E241 E242 E243 E244 E245 E246 E247 E248 E249 E250 E251 E252 E253 E254 E255 E256 E257 E258 E259 E260 E261 E262 E263 E264 E265 E266 E267 E268 E269 E270 E271 E272 E273 E274 E275 E276 E277 E278 E279 E280 E281 E282 E283 E284 E285 E286 E287 E288 E289 E290 E291 E292 E293 E294 E295 E296 E297 E298 E299 E300 E301">
       <formula1>"En attente,Accepté,Refusé"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1657,9 +1690,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.96875" customWidth="1"/>
     <col min="2" max="2" width="32.015625" customWidth="1"/>
@@ -1762,7 +1794,7 @@
       <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="10">
         <f>B7*B6+B8</f>
         <v>6</v>
       </c>
@@ -1771,7 +1803,7 @@
       <c r="A16" t="s">
         <v>33</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="0">
         <f>B15*Paramètres!B2</f>
         <v>300</v>
       </c>
@@ -1780,7 +1812,7 @@
       <c r="A17" t="s">
         <v>34</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="0">
         <f>B9*Paramètres!B3</f>
         <v>20</v>
       </c>
@@ -1789,7 +1821,7 @@
       <c r="A18" t="s">
         <v>35</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="0">
         <f>B11*Paramètres!B5/100</f>
         <v>0</v>
       </c>
@@ -1798,7 +1830,7 @@
       <c r="A19" t="s">
         <v>36</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="0">
         <f>B16+B17+B10+B11</f>
         <v>420</v>
       </c>
@@ -1807,7 +1839,7 @@
       <c r="A20" t="s">
         <v>37</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="0">
         <f>B19*Paramètres!B4/100</f>
         <v>42</v>
       </c>
@@ -1816,7 +1848,7 @@
       <c r="A21" t="s">
         <v>38</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="0">
         <f>B19+B20+B18</f>
         <v>462</v>
       </c>
@@ -1825,7 +1857,7 @@
       <c r="A22" t="s">
         <v>39</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="0">
         <f>ROUND(B21/5,0)*5</f>
         <v>460</v>
       </c>
@@ -1834,12 +1866,12 @@
       <c r="A23" t="s">
         <v>40</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="0">
         <f>IF(B3=0,0,B22/B3)</f>
-        <v>10.222222222222221</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="41.25" x14ac:dyDescent="0.2">
+        <v>10.2222222222222</v>
+      </c>
+    </row>
+    <row ht="41.25" r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -1853,9 +1885,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.015625" customWidth="1"/>
     <col min="2" max="2" width="69.94921875" customWidth="1"/>
@@ -1939,9 +1970,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.99609375" customWidth="1"/>
     <col min="2" max="2" width="27.98046875" customWidth="1"/>
@@ -2071,7 +2101,7 @@
         <v>258.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="18.75" x14ac:dyDescent="0.2">
+    <row ht="18.75" r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>64</v>
       </c>
@@ -2111,9 +2141,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="11" width="18.0234375" customWidth="1"/>
   </cols>
@@ -2154,9 +2183,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K500" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:K500"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H500" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H500">
       <formula1>"À faire,Devis envoyé,Accepté,Refusé,Terminé,À relancer"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2165,9 +2194,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:K501"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="11" width="18.0234375" customWidth="1"/>
   </cols>
@@ -11708,9 +11736,9 @@
       <c r="K501" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K500" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:K500"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K500" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K500">
       <formula1>"Brouillon,Envoyé,Accepté,Refusé,Terminé"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11719,9 +11747,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="16.0078125" customWidth="1"/>
   </cols>
@@ -11938,9 +11965,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="22.05859375" customWidth="1"/>
   </cols>
@@ -11966,9 +11992,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1000" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <autoFilter ref="A1:F1000"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B1000" xr:uid="{00000000-0002-0000-0700-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B1000">
       <formula1>"Carburant,Duster,Assurance,Remorque,Déchèterie,Matériel,Communication,Téléphone,Comptabilité,Autre"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11977,15 +12003,14 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.99609375" customWidth="1"/>
     <col min="2" max="2" width="23.9453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.2">
+    <row ht="21" r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>107</v>
       </c>
@@ -12063,7 +12088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="54.75" x14ac:dyDescent="0.2">
+    <row ht="54.75" r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>66</v>
       </c>
